--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.00846748557122654</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31887083</v>
+        <v>4267681</v>
       </c>
       <c r="L2" t="n">
-        <v>18108811</v>
+        <v>1973717</v>
       </c>
       <c r="M2" t="n">
-        <v>4497619</v>
+        <v>428380</v>
       </c>
       <c r="N2" t="n">
-        <v>245391</v>
+        <v>13503</v>
       </c>
       <c r="O2" t="n">
-        <v>2689709</v>
+        <v>269040</v>
       </c>
       <c r="P2" t="n">
-        <v>1054990</v>
+        <v>82915</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999911189079285</v>
+        <v>0.9999809265136719</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8878327608108521</v>
+        <v>0.786260724067688</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7825811505317688</v>
+        <v>0.6335515379905701</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7331503033638</v>
+        <v>0.5361143350601196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4310860633850098</v>
+        <v>0.1023132801055908</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7718641757965088</v>
+        <v>0.5586807727813721</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8488317131996155</v>
+        <v>0.7287821173667908</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029527753233312</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>31887083</v>
+        <v>4267681</v>
       </c>
       <c r="E3" t="n">
-        <v>3434200</v>
+        <v>742593</v>
       </c>
       <c r="F3" t="n">
-        <v>66902</v>
+        <v>22595</v>
       </c>
       <c r="G3" t="n">
-        <v>7671</v>
+        <v>2386</v>
       </c>
       <c r="H3" t="n">
-        <v>4463</v>
+        <v>1699</v>
       </c>
       <c r="I3" t="n">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="J3" t="n">
-        <v>70486945</v>
+        <v>10069499</v>
       </c>
       <c r="K3" t="n">
-        <v>75482833</v>
+        <v>10218804</v>
       </c>
       <c r="L3" t="n">
-        <v>86884326</v>
+        <v>11972516</v>
       </c>
       <c r="M3" t="n">
-        <v>106731433</v>
+        <v>15108255</v>
       </c>
       <c r="N3" t="n">
-        <v>113962433</v>
+        <v>16207891</v>
       </c>
       <c r="O3" t="n">
-        <v>110549708</v>
+        <v>15693015</v>
       </c>
       <c r="P3" t="n">
-        <v>113370585</v>
+        <v>16191636</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9007495641708374</v>
+        <v>0.8472566604614258</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7874548435211182</v>
+        <v>0.5977557301521301</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6873375177383423</v>
+        <v>0.4571439623832703</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3921744525432587</v>
+        <v>0.1506442725658417</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7539882063865662</v>
+        <v>0.5270519852638245</v>
       </c>
       <c r="W3" t="n">
-        <v>0.779434859752655</v>
+        <v>0.428485780954361</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03201304320695698</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3788030</v>
+        <v>1079016</v>
       </c>
       <c r="E4" t="n">
-        <v>18108811</v>
+        <v>1973717</v>
       </c>
       <c r="F4" t="n">
-        <v>961138</v>
+        <v>203610</v>
       </c>
       <c r="G4" t="n">
-        <v>44218</v>
+        <v>16850</v>
       </c>
       <c r="H4" t="n">
-        <v>87246</v>
+        <v>27112</v>
       </c>
       <c r="I4" t="n">
-        <v>7178</v>
+        <v>1569</v>
       </c>
       <c r="J4" t="n">
-        <v>395</v>
+        <v>121</v>
       </c>
       <c r="K4" t="n">
-        <v>4028559</v>
+        <v>1160138</v>
       </c>
       <c r="L4" t="n">
-        <v>5031040</v>
+        <v>1141605</v>
       </c>
       <c r="M4" t="n">
-        <v>1637029</v>
+        <v>370666</v>
       </c>
       <c r="N4" t="n">
-        <v>323848</v>
+        <v>118474</v>
       </c>
       <c r="O4" t="n">
-        <v>794983</v>
+        <v>212523</v>
       </c>
       <c r="P4" t="n">
-        <v>187883</v>
+        <v>30857</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999904632568359</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8942445516586304</v>
+        <v>0.8156198859214783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7850104570388794</v>
+        <v>0.6151332855224609</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7095050811767578</v>
+        <v>0.4934898018836975</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4107106626033783</v>
+        <v>0.1218616291880608</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7628214359283447</v>
+        <v>0.5424057245254517</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8126544952392578</v>
+        <v>0.5396724343299866</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>159961</v>
+        <v>58549</v>
       </c>
       <c r="E5" t="n">
-        <v>1347621</v>
+        <v>325387</v>
       </c>
       <c r="F5" t="n">
-        <v>4497619</v>
+        <v>428380</v>
       </c>
       <c r="G5" t="n">
-        <v>115743</v>
+        <v>35299</v>
       </c>
       <c r="H5" t="n">
-        <v>389711</v>
+        <v>81975</v>
       </c>
       <c r="I5" t="n">
-        <v>32851</v>
+        <v>7469</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3513525</v>
+        <v>769377</v>
       </c>
       <c r="L5" t="n">
-        <v>4887823</v>
+        <v>1328162</v>
       </c>
       <c r="M5" t="n">
-        <v>2045919</v>
+        <v>508699</v>
       </c>
       <c r="N5" t="n">
-        <v>380328</v>
+        <v>76132</v>
       </c>
       <c r="O5" t="n">
-        <v>877600</v>
+        <v>241422</v>
       </c>
       <c r="P5" t="n">
-        <v>298542</v>
+        <v>110592</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999996542930603</v>
+        <v>0.9999926090240479</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9343664646148682</v>
+        <v>0.8824613094329834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9136829376220703</v>
+        <v>0.8495512008666992</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9679498672485352</v>
+        <v>0.9464324712753296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938720464706421</v>
+        <v>0.9881453514099121</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9854446649551392</v>
+        <v>0.9723473787307739</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957669973373413</v>
+        <v>0.9913834929466248</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>74952</v>
+        <v>18794</v>
       </c>
       <c r="E6" t="n">
-        <v>116228</v>
+        <v>21046</v>
       </c>
       <c r="F6" t="n">
-        <v>123941</v>
+        <v>25445</v>
       </c>
       <c r="G6" t="n">
-        <v>245391</v>
+        <v>13503</v>
       </c>
       <c r="H6" t="n">
-        <v>58882</v>
+        <v>9822</v>
       </c>
       <c r="I6" t="n">
-        <v>6212</v>
+        <v>991</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>5355</v>
+        <v>3679</v>
       </c>
       <c r="E7" t="n">
-        <v>124516</v>
+        <v>48531</v>
       </c>
       <c r="F7" t="n">
-        <v>461549</v>
+        <v>110262</v>
       </c>
       <c r="G7" t="n">
-        <v>144759</v>
+        <v>58194</v>
       </c>
       <c r="H7" t="n">
-        <v>2689709</v>
+        <v>269040</v>
       </c>
       <c r="I7" t="n">
-        <v>141382</v>
+        <v>20744</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>261</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>8475</v>
+        <v>4048</v>
       </c>
       <c r="F8" t="n">
-        <v>23499</v>
+        <v>8754</v>
       </c>
       <c r="G8" t="n">
-        <v>11457</v>
+        <v>5745</v>
       </c>
       <c r="H8" t="n">
-        <v>254681</v>
+        <v>91915</v>
       </c>
       <c r="I8" t="n">
-        <v>1054990</v>
+        <v>82915</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
